--- a/Rezepte/Mürbeteig.xlsx
+++ b/Rezepte/Mürbeteig.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -41,72 +42,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -189,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -253,32 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -305,24 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -334,142 +244,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -479,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.7109375" customWidth="1" style="4" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
@@ -493,293 +424,278 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Maximal gleichzeitig herstellbare Menge</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rezept:</t>
+          <t>1x</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Haltbarkeit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1 Woche (Kühlung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Butter 1h vorher aus Kühlung nehmen | Fertigen Teig über Nacht kühlen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Zutat</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Zucker</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Butter</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Salz</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Zitronenaroma</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Vanillearoma</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Vollei</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C13" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Weizenmehl</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maximal gleichtzeitig herzustellende Menge:</t>
-        </is>
+          <t>Weizenmehl</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>1x Grundrezept</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Herstellung:</t>
-        </is>
-      </c>
-    </row>
+          <t>Zeitaufwand aktiv</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zeitaufwand passiv</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Butter auf Raumtemperatur temperieren</t>
+          <t>Portionsgrößen</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zucker, Butter und Aromen glatt arbeiten</t>
+          <t>Backform</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gramm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vollei auf drei Mal hinzugeben, glatt arbeiten</t>
-        </is>
+          <t>Tartelette</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mehl auf ein Mal hinzugeben, kurz unterkneten</t>
-        </is>
+          <t>30x20 Schnitte</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teig in Frischhaltefolie einpacken</t>
-        </is>
+          <t>Kuchenform</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Über Nacht kühlen, erst danach Ausrollen</t>
-        </is>
+          <t>Mürbeteig rund</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="24"/>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Portionsgrößen:</t>
+          <t>Ausrollzeiten</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Backform</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Menge</t>
+          <t>min pro Stück</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Tartelette</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>40</v>
+      <c r="C27" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>30x20 Schnitte</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Kuchenform</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>350</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Mürbeteig rund</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31"/>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Backen:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Im Rational iHexagon bei 180°C Hitze ca. 7-9 Minuten backen</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Haltbarkeit:</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>gebacken</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 Wochen </t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ungebacken</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3 Tage</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Zeitaufwand aktiv:</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Zeitaufwand passiv:</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0 min</t>
-        </is>
+          <t>Anbackzeit (min)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>